--- a/src/attributions/attributions_ig_traj_451.xlsx
+++ b/src/attributions/attributions_ig_traj_451.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.05093390072276603</v>
+        <v>-0.04390659277869661</v>
       </c>
       <c r="B3" t="n">
-        <v>0.475799005221293</v>
+        <v>0.05247917600405811</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,13 +1580,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.07858629896245023</v>
+        <v>0.02054122094714309</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1007166870559984</v>
+        <v>-0.04128470921468516</v>
       </c>
       <c r="K3" t="n">
-        <v>0.456821138017877</v>
+        <v>0.09511280943642673</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1265729949260693</v>
+        <v>-0.001436792970578477</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1622,79 +1622,79 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04967646663717615</v>
+        <v>0.01957623788237676</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2901777066111002</v>
+        <v>0.02122588678435956</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3208066734843791</v>
+        <v>-0.004440289383463041</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1543097335915174</v>
+        <v>0.01653201776957852</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1957105908339999</v>
+        <v>0.01596229744487669</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.2282067854058596</v>
+        <v>-0.03624450358984076</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.1084674829811471</v>
+        <v>-0.00900514544944654</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1705754645917417</v>
+        <v>0.03576833098784371</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1338057554457024</v>
+        <v>0.02957576904560265</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
@@ -1703,25 +1703,25 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07040931267697702</v>
+        <v>-0.03294413896172357</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.7561953424520188</v>
+        <v>0.1727205319998392</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4684624642265953</v>
+        <v>-0.02911349593640179</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
@@ -1730,52 +1730,52 @@
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01456457228416877</v>
+        <v>-0.02737228884902246</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.03170229028834366</v>
+        <v>-0.02336661325882902</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2119721528148338</v>
+        <v>-0.01040143164625546</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01904219168104138</v>
+        <v>0.01458137562429257</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.144595237645191</v>
+        <v>0.05847822279119935</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1715021136180842</v>
+        <v>0.04094138546429402</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,37 +1784,37 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.06802805233351129</v>
+        <v>0.004287931704050269</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.4037657231737623</v>
+        <v>0.1202702663263878</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2126677662863432</v>
+        <v>0.02778555599199367</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.004302540559906926</v>
+        <v>0.0195898558132884</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.2246324585098921</v>
+        <v>-0.03556774438362142</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
@@ -1823,64 +1823,64 @@
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01446525610453669</v>
+        <v>-0.01851128346955478</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.1264187734149223</v>
+        <v>-0.01890366279956708</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.02857780397752413</v>
+        <v>-0.05645289805379834</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1914748148426732</v>
+        <v>-0.01643443008378369</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.005073114298277574</v>
+        <v>0.006328517715558904</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.2318030031216413</v>
+        <v>-0.03548678600377766</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.01505801704147681</v>
+        <v>-0.03483834457364218</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.02543379250642754</v>
+        <v>-0.006099816155082535</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1707992186646124</v>
+        <v>-0.0554303547440395</v>
       </c>
       <c r="DG3" t="n">
         <v>-0</v>
@@ -1904,34 +1904,34 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03283925066654115</v>
+        <v>-0.04395406158087862</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.04808398920772963</v>
+        <v>-0.01338490154668309</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.1065879119745777</v>
+        <v>0.001410599087877311</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1605228938849021</v>
+        <v>-0.01732670828522583</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,55 +1940,55 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.01705351802338204</v>
+        <v>0.02605080358594333</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.3072126945723512</v>
+        <v>-0.06515652642951442</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.03964421304942762</v>
+        <v>-0.04518240986320208</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.03124007554731149</v>
+        <v>0.002460304792489962</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.08976672198031055</v>
+        <v>0.01066667106744059</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1275042230048829</v>
+        <v>-0.03441188427234139</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
@@ -2000,37 +2000,37 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.006794714323435035</v>
+        <v>-0.0004044839665682274</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.2474700857252338</v>
+        <v>-0.01977822012900287</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.04988320517283035</v>
+        <v>-0.0194280161835383</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.04535436446639774</v>
+        <v>0.0131936392225351</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.2489629393170266</v>
+        <v>-0.05519660524236829</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,25 +2039,25 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.0371456924907347</v>
+        <v>-0.03542712965415112</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03551315682009513</v>
+        <v>0.0102665618942733</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.07528825000802508</v>
+        <v>0.03109009239828956</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.06844835795705002</v>
+        <v>-0.007592565903497906</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.07042825218692311</v>
+        <v>0.06613984280134128</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.2064307159417071</v>
+        <v>-0.025383255751599</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,13 +2093,13 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.09894136974426099</v>
+        <v>0.04164185963444379</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
@@ -2108,31 +2108,31 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.1249119096118465</v>
+        <v>0.03040301441094533</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1335267278520729</v>
+        <v>-0.02165361486966322</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,46 +2709,46 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4461025768775616</v>
+        <v>0.4148850587886191</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1083729166489292</v>
+        <v>-0.2294767226322655</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01526540388580807</v>
+        <v>-0.05684916499038312</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3471712523588874</v>
+        <v>0.4243749199807931</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1734754621345083</v>
+        <v>-0.416852412002039</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06792462339708931</v>
+        <v>-0.1462288526580902</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
@@ -2757,163 +2757,163 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1865566861617528</v>
+        <v>0.1720976148809289</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.002949501473248121</v>
+        <v>-0.01620817947713438</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05522171548875771</v>
+        <v>-0.008514673813173362</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.145059086688476</v>
+        <v>-0.1505480228281362</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02394728536052072</v>
+        <v>-0.3362315353538967</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05530551376897785</v>
+        <v>-0.1176974895614698</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0241097536254115</v>
+        <v>0.1927518547741665</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1004112692247009</v>
+        <v>-0.09984913291145558</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08949816320440851</v>
+        <v>0.1355024453697666</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5158931448493737</v>
+        <v>0.5351234663066329</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.007546178419425936</v>
+        <v>-0.3000656862900616</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2410801838932891</v>
+        <v>-0.4316264664779721</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.07279977000616558</v>
+        <v>0.1035357177150814</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.09515203252986354</v>
+        <v>-0.134921305643682</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1486815915853811</v>
+        <v>0.00142545325567207</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04681204642612063</v>
+        <v>-0.02169314060662453</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.705973503843886e-10</v>
+        <v>5.386699322130086e-11</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.222061037808811</v>
+        <v>-0.001005216393566043</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2683692036402678</v>
+        <v>0.5016721382756321</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01778261594473974</v>
+        <v>-0.1894617179113769</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.08096117524829691</v>
+        <v>-0.07565204165438766</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1609851094912118</v>
+        <v>-0.1903088370927919</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01433514702262619</v>
+        <v>0.2301575294742458</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02930853370862318</v>
+        <v>-0.004511147591194205</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.00498121264135085</v>
+        <v>-0.2048113019719814</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.08682986956711741</v>
+        <v>0.2173045672188026</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.104215287766951</v>
+        <v>0.06440427803747875</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1564317616100308</v>
+        <v>-0.2008062903164174</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04772078569033593</v>
+        <v>0.2437116352128771</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03381582168923555</v>
+        <v>-0.002765563976859301</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1142245871260718</v>
+        <v>-0.2334508047064076</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01007932476176376</v>
+        <v>0.2381661586629637</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.03811260047098777</v>
+        <v>0.02755388094132537</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3060,43 +3060,43 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.03917864747904748</v>
+        <v>-0.05124787557699658</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1451341584822357</v>
+        <v>0.08801601986785135</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03554281187307803</v>
+        <v>0.06206680098441876</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1121119859220016</v>
+        <v>0.01807553083597184</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.007627429971434789</v>
+        <v>0.16674476726642</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02345987241870664</v>
+        <v>-0.06044296972840806</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
@@ -3105,58 +3105,58 @@
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1134454180061953</v>
+        <v>-0.1509606834778117</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.02156383731138341</v>
+        <v>0.198938073255531</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06781767150673111</v>
+        <v>0.006355426545636586</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1508341557490784</v>
+        <v>-0.1982744980488148</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1135641325666964</v>
+        <v>-0.1289495186967319</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.09567384264494608</v>
+        <v>-0.1103372236898407</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.163438702585384</v>
+        <v>-0.2320038502657592</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01085974533617611</v>
+        <v>0.2780896625540955</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.03225190352710168</v>
+        <v>-0.02818570829429073</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3195,79 +3195,79 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0003476739888546743</v>
+        <v>-0.1606675704611513</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.07011973266989037</v>
+        <v>0.1211828232725485</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002661562476595198</v>
+        <v>-0.02924847032550033</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001459208311750294</v>
+        <v>-0.09284312632748536</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.05748009201967896</v>
+        <v>0.2857757535701946</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06159445688183588</v>
+        <v>0.3864124623622391</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.009620919826991264</v>
+        <v>-0.1754730637792231</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.08364623296503529</v>
+        <v>0.1002276655382495</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,25 +3275,25 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.144617707059109</v>
+        <v>-0.0109277941742054</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3042053029400887</v>
+        <v>0.03223694759379327</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08431730231640004</v>
+        <v>-0.005665732327790643</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1059829295022069</v>
+        <v>-0.008920508854974781</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2874681480306256</v>
+        <v>0.0467931129054026</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1596926369861656</v>
+        <v>-0.008832007190436855</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,79 +3329,79 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01670687852925237</v>
+        <v>0.009669392937734628</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2425312303584033</v>
+        <v>0.007534124209191683</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.14643584496817</v>
+        <v>-0.004318145389787691</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.13474207947463</v>
+        <v>0.003902831723182589</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3036688574518418</v>
+        <v>-0.00405972395420055</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01848709005060308</v>
+        <v>-0.001794986390647473</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.002621871605536885</v>
+        <v>-0.0009609308535002119</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1580104158255896</v>
+        <v>0.01118269229067184</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08781186415590195</v>
+        <v>0.004774885399851238</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,37 +3410,37 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.05056865350351718</v>
+        <v>-0.005077708261246175</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.386830755054783</v>
+        <v>0.03659478163055387</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2982198295723554</v>
+        <v>-0.01372557229560448</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0741758441684881</v>
+        <v>-0.01228720560208019</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.05336678116843247</v>
+        <v>0.005535156057662327</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.2494631019787794</v>
+        <v>-0.005426190769821886</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.07285536349701917</v>
+        <v>-0.005935827380371035</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1526724985321976</v>
+        <v>0.002566628053082425</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.04668136733124158</v>
+        <v>0.02412800462832786</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,19 +3491,19 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.04917897564230676</v>
+        <v>0.007187043714998313</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3193533495980883</v>
+        <v>0.0320920156510458</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.08432089979291424</v>
+        <v>-0.0003413393510630068</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3515,13 +3515,13 @@
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.04205585847499804</v>
+        <v>0.004650444685082459</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1157626120994994</v>
+        <v>-0.01436220589256007</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,25 +3530,25 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0109287611628473</v>
+        <v>0.001684071056523186</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.06391396906845283</v>
+        <v>-0.0006432979332485708</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.005105979958593941</v>
+        <v>-0.01302685212274453</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
@@ -3557,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.09400518772718272</v>
+        <v>-0.001206004774271806</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3569,13 +3569,13 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.02564948640172982</v>
+        <v>0.002352642634981614</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1298235554065021</v>
+        <v>-0.01452394543909868</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
@@ -3584,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.001692438394052241</v>
+        <v>-7.185491301938951e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.04702922460499681</v>
+        <v>0.00183713136934989</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1553822932237132</v>
+        <v>-0.01749161309836041</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,25 +3611,25 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05212611830189312</v>
+        <v>-0.001343051961301969</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.02168845502443478</v>
+        <v>-0.0008001984701802754</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.04105362614806844</v>
+        <v>-0.01398343377919435</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,7 +3638,7 @@
         <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.06141383808416896</v>
+        <v>-0.003268047452802776</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3653,91 +3653,91 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.007175038842473454</v>
+        <v>0.01044530239195106</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.1059788661015325</v>
+        <v>0.01290781012693562</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.00409533620788957</v>
+        <v>-0.005356241534617273</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.08733345989379473</v>
+        <v>-0.0008227443384974075</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.008101806116608318</v>
+        <v>-0.006486153796969812</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01449782560123855</v>
+        <v>-0.005522300450092211</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.05112267127667793</v>
+        <v>-0.0003743358810855538</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1430421951598392</v>
+        <v>-0.0008094214594356689</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.008881314172604522</v>
+        <v>-0.00334808553517577</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.02531777779234149</v>
+        <v>0.00379329020368831</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1358639342966988</v>
+        <v>-0.0172279382473324</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,10 +3746,10 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05072732527754874</v>
+        <v>-0.001707906756296516</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.05077363708931815</v>
+        <v>-0.003799521936873067</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.05952363317205129</v>
+        <v>-0.006415985084411518</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,7 +3773,7 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.08322575456290615</v>
+        <v>0.005821837892228653</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0.03517861370778907</v>
+        <v>0.01797817763382599</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.2278223760770041</v>
+        <v>-0.00714827221352111</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1386650757347677</v>
+        <v>0.01178823142416014</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0.09262923117954405</v>
+        <v>0.00387050087233019</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01069600864067825</v>
+        <v>-0.0123609871707846</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,16 +3830,16 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4270753249631639</v>
+        <v>0.8485114701432367</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1960931237924586</v>
+        <v>-0.6135635877293918</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0771616866793</v>
+        <v>-0.2651548633019827</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,73 +3874,73 @@
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3363957818941062</v>
+        <v>0.8128567886548979</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2348528728529808</v>
+        <v>-1.01180106365442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.104396038570113</v>
+        <v>-0.4312252974449268</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1446935178741774</v>
+        <v>0.2810154968578865</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004742099518890276</v>
+        <v>-0.03839383661241748</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1141965487985816</v>
+        <v>-0.03859788233021835</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1448897834155375</v>
+        <v>0.06236555779377152</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.009202354170350526</v>
+        <v>-0.229738439560574</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.06688332678711209</v>
+        <v>-0.05462589620155506</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3952,73 +3952,73 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.06247382333808175</v>
+        <v>0.4739931622748794</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.07485594790955916</v>
+        <v>-0.07275888414016408</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0416297262119171</v>
+        <v>0.3637360641014691</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5960330250386856</v>
+        <v>1.14496373097242</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.02530861934199411</v>
+        <v>-0.5324278542118958</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1413444318850269</v>
+        <v>-0.3865516648096158</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0150736661268544</v>
+        <v>-0.1232590218994195</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1207116079820369</v>
+        <v>-0.05255471796945609</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1646581374031354</v>
+        <v>-0.1622522548724384</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4033,25 +4033,25 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02505844970128879</v>
+        <v>-0.1294139553231844</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06041767441340998</v>
+        <v>0.05883184712980638</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1387916858850762</v>
+        <v>0.1208925098752512</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,46 +4063,46 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3206112096901577</v>
+        <v>0.8671596145323561</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02048998199641618</v>
+        <v>-0.4825981127875875</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1021425784936853</v>
+        <v>-0.1145796655873291</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1284401003112307</v>
+        <v>-0.3907726678489744</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05025560469902627</v>
+        <v>0.3229594697743453</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03097483435299095</v>
+        <v>0.04061232951554521</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02102969667176206</v>
+        <v>-0.3117691675471356</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0651183625688065</v>
+        <v>0.171965625420332</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1392244560661554</v>
+        <v>0.09059450705193618</v>
       </c>
       <c r="CR7" t="n">
         <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
@@ -4141,25 +4141,25 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1152670482514614</v>
+        <v>-0.4305817782492873</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.07275611263430364</v>
+        <v>0.3371261465028398</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0251315938255113</v>
+        <v>0.08747266681329929</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,22 +4171,22 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1155516713978643</v>
+        <v>-0.5832014195793099</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.06227850095790969</v>
+        <v>0.4538232325369542</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0353095207690951</v>
+        <v>-0.10267869587697</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,25 +4198,25 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07950320439014877</v>
+        <v>-0.1929344443761666</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.04186717131372986</v>
+        <v>0.1576239242508045</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06624154548672159</v>
+        <v>-0.08739594444433864</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,25 +4225,25 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04895921925588016</v>
+        <v>0.1751955146064237</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.02108656799314412</v>
+        <v>0.1957539501088083</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03230507657070937</v>
+        <v>-0.08745764024207725</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,25 +4252,25 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.09971976312390379</v>
+        <v>-0.2751380470181516</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0608750527775274</v>
+        <v>0.2653240194806165</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1249348268990969</v>
+        <v>0.06770768648579024</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08636700721743262</v>
+        <v>-0.3542102810285016</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09419431536303698</v>
+        <v>0.2730646420908658</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.08536859812108619</v>
+        <v>0.004232024223151071</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,106 +4306,106 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1266260245810478</v>
+        <v>-0.4653579807442564</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.06676486374684745</v>
+        <v>0.3694700835766026</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03428298654327701</v>
+        <v>0.05599739322818891</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01329534274654105</v>
+        <v>-0.179951968209028</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.02550261952532894</v>
+        <v>-0.02833386841679646</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01585341661976099</v>
+        <v>0.01390961805906972</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.005880072685734675</v>
+        <v>-0.3778187262572087</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.1006695225847066</v>
+        <v>0.5795400253801049</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1442931469397952</v>
+        <v>0.1286575251940759</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.04885786719379055</v>
+        <v>-0.3301736581074515</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.04284880198243489</v>
+        <v>0.1118105894631612</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1678359723708908</v>
+        <v>0.5206729045739684</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03033777101907763</v>
+        <v>-0.01490131356730625</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1040325801905506</v>
+        <v>-0.2110851942976101</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1310649498054584</v>
+        <v>0.6039899629975828</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,37 +4452,37 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02104772910727366</v>
+        <v>-0.1690384000232014</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1182398148752345</v>
+        <v>-0.2238328863433155</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02956148166151028</v>
+        <v>0.1087740543204342</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01334726600424503</v>
+        <v>-0.0683085912119388</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.008876243850304789</v>
+        <v>-0.08096373624768512</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4497,49 +4497,49 @@
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02882597202595967</v>
+        <v>0.07408867258421317</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01338990027246036</v>
+        <v>-0.2485114202287084</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.02344038902738942</v>
+        <v>-0.06794761111901183</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01637069526011906</v>
+        <v>0.1485013583354761</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006840173974603005</v>
+        <v>0.04667219224223276</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05586838190952034</v>
+        <v>-0.1312387544459742</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,25 +4548,25 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1464897523091824</v>
+        <v>0.8226626522611349</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01598552056760086</v>
+        <v>-0.1790249681980609</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1306808005670502</v>
+        <v>-0.2073335225789034</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4575,10 +4575,10 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0673261848231566</v>
+        <v>-0.02581159133415223</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,40 +4587,40 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.02896992842094685</v>
+        <v>-0.08151319478555537</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0358211680048967</v>
+        <v>-0.1026476961965322</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0394847443525744</v>
+        <v>0.08941189223710164</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01999238570669076</v>
+        <v>0.09494531333415918</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.005437126003285028</v>
+        <v>0.04982209812182049</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,7 +4632,7 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07775430141673513</v>
+        <v>0.5196266701339757</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01328005399864363</v>
+        <v>-0.04185173941572392</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.05656129298303352</v>
+        <v>-0.1983277921591237</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4656,28 +4656,28 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04269844331977474</v>
+        <v>-0.2448279226603646</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.001129584504083976</v>
+        <v>0.006648490103817029</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03342316812401144</v>
+        <v>0.1442960692493404</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
         <v>0</v>
@@ -4686,52 +4686,52 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.009076260677597443</v>
+        <v>-0.2621871842192179</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.004409190026352442</v>
+        <v>0.07753242078660247</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008494679147056211</v>
+        <v>0.1200693535698551</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03540505602767957</v>
+        <v>-0.232145107275684</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.00193201638450198</v>
+        <v>-0.0121867052275593</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.03815295937088038</v>
+        <v>0.1273202058173542</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.03468579059073126</v>
+        <v>-0.07520918701380258</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03749238765348856</v>
+        <v>-0.2441016213666764</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.03278153150182752</v>
+        <v>0.06501208171366926</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,52 +4761,52 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01132113686770578</v>
+        <v>-0.08603490254918844</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01276490246213354</v>
+        <v>0.01835784950699929</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.00179942779728434</v>
+        <v>0.06567475150411202</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.04213931683213012</v>
+        <v>0.06326668366206256</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01051588979404559</v>
+        <v>-0.004522867953881685</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01260437734599104</v>
+        <v>-0.0442786529659828</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,121 +4815,121 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02803988176765475</v>
+        <v>-0.07797387968973848</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0127694229464104</v>
+        <v>-0.07684631748266768</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01949256791267902</v>
+        <v>0.1030256156825658</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01206297250833705</v>
+        <v>-0.1400719169692648</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0008251581147397228</v>
+        <v>-0.1369845572955772</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01188845542362808</v>
+        <v>0.04773363769801198</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03696095518477188</v>
+        <v>-0.2576355754598741</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.005047873037353013</v>
+        <v>-0.03892475862779161</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0376297456756482</v>
+        <v>0.124663172485026</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.008347755896053527</v>
+        <v>-0.2334858988223528</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.0257392736257557</v>
+        <v>0.06352762147357514</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.05206297992885468</v>
+        <v>0.1364275189488117</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0223412609147632</v>
+        <v>-0.1972173822266088</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,10 +4938,10 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.01571667868067597</v>
+        <v>0.006933553557220612</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.004039893745518369</v>
+        <v>0.01172190638763567</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4953,22 +4953,22 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01934436599291003</v>
+        <v>-0.1126082917801524</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04783219380806054</v>
+        <v>0.01916314713617157</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,51 +4977,51 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2829030822561816</v>
+        <v>0.5981954857912927</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.106882356227446</v>
+        <v>-0.2969623673898679</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05920424330648071</v>
+        <v>-0.152155266516386</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1985561162599711</v>
+        <v>0.538546278416781</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1244889898673389</v>
+        <v>-0.5326278635917765</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1015229855089371</v>
+        <v>-0.2561143647256803</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,28 +5030,28 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08902387069141132</v>
+        <v>0.1554613546795509</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.008345487945828048</v>
+        <v>0.002205172999481377</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02709405342550296</v>
+        <v>-0.09439070936124058</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,100 +5063,100 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.09290962283167808</v>
+        <v>0.01906951628782034</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02093973728870638</v>
+        <v>-0.1398675776832299</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.03221064699103029</v>
+        <v>-0.1438768527673913</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01036502800341894</v>
+        <v>0.2386020487135272</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03202702756739855</v>
+        <v>0.02132374278314224</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.0783824407729487</v>
+        <v>0.05902680804338208</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3986924455510888</v>
+        <v>0.5852428604639924</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.04397610491404055</v>
+        <v>-0.3104590761399194</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.09853368166183137</v>
+        <v>-0.4642981992816391</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01169047931203164</v>
+        <v>0.05209611304041871</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.04783534075302497</v>
+        <v>-0.06780235409583231</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1178161943541349</v>
+        <v>0.01076075548536272</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09538996151015593</v>
+        <v>0.02972540205276209</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03073134803017336</v>
+        <v>0.02940798838184968</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1410039632409338</v>
+        <v>0.1351977678785467</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,46 +5201,46 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2102487036040516</v>
+        <v>0.4403115403167604</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.008273904244236501</v>
+        <v>-0.259074877889684</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04537253750179957</v>
+        <v>-0.1551307854774424</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.07210606418175672</v>
+        <v>-0.1964289295213447</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02047882047581454</v>
+        <v>0.2223712556752468</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.001181260680015966</v>
+        <v>0.04272184258573923</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.03819016241797305</v>
+        <v>-0.1362269357877935</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.03362698419554005</v>
+        <v>0.06898651704637977</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.05681766082921248</v>
+        <v>0.05497939866309592</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,31 +5276,31 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05868451119666628</v>
+        <v>-0.2061038364770198</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0402487234414329</v>
+        <v>0.2365535037724375</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.005457970064337354</v>
+        <v>0.04052883054702571</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03424240402188736</v>
+        <v>-0.1949056205203407</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1047549109687223</v>
+        <v>0.1806397939209052</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.009276711543831102</v>
+        <v>-0.01804980322185027</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,103 +5336,103 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.04391554057209627</v>
+        <v>-0.1101427220093671</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.07208994428797939</v>
+        <v>0.1115558527791647</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0085384961174251</v>
+        <v>-0.1076252999418755</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.04589782134249063</v>
+        <v>0.06113390419464192</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.01051769513848558</v>
+        <v>0.1409379520924394</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.0179114608825316</v>
+        <v>-0.07777282038067147</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.06366287972859422</v>
+        <v>-0.1071813773660414</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.0888163662525399</v>
+        <v>-0.2536279676168143</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.07975363993594663</v>
+        <v>0.02653403315682898</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06334898216225113</v>
+        <v>-0.1754495076285545</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.07284506306008492</v>
+        <v>0.1520474368824491</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02143337066612031</v>
+        <v>-0.03719423229834483</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,46 +5441,46 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05955299015010749</v>
+        <v>-0.2312121454210484</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03590625059803997</v>
+        <v>0.2443115696245191</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.006891075062242417</v>
+        <v>0.01683672857335803</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.05071590473610993</v>
+        <v>-0.0706967752439655</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.01509688872184695</v>
+        <v>-0.02162957509562408</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03171114409774673</v>
+        <v>0.09576730474215327</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,25 +5489,25 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.03808684757421084</v>
+        <v>-0.1768278968121974</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01025282672421068</v>
+        <v>0.3921348451500837</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.06121400548820744</v>
+        <v>0.1488094433590491</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.01502366942579967</v>
+        <v>-0.16531925826145</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.007216104718020705</v>
+        <v>0.09589830227791712</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,52 +5551,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.06350635857820673</v>
+        <v>-0.08921700494951078</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1813794252132459</v>
+        <v>0.03529369014776861</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1020727415252537</v>
+        <v>0.008394089954063716</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08740937797464801</v>
+        <v>-0.1192482981592166</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.01461278306059381</v>
+        <v>-0.07856723916570903</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1125921596923515</v>
+        <v>-0.01522567980485038</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03301898456953582</v>
+        <v>-0.03772692177581148</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0875999402090938</v>
+        <v>-0.2501364219143496</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5605,79 +5605,79 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02590053984796397</v>
+        <v>0.03126988627722301</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08484073442047946</v>
+        <v>-0.01904206798569518</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.06914635647235486</v>
+        <v>-0.07888873248838996</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.04939158663306453</v>
+        <v>0.1370990681950888</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02502762096434809</v>
+        <v>0.1795914455367535</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.06951484382384486</v>
+        <v>-0.1630156226810618</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.04693452167304587</v>
+        <v>-0.3158427392408678</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.0114151315738517</v>
+        <v>-0.0761055647885253</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.01595745576516778</v>
+        <v>0.001682482737428896</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.05014287743000098</v>
+        <v>-0.06419902958051055</v>
       </c>
       <c r="AN10" t="n">
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02585489661122989</v>
+        <v>-0.1895237172776262</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.01653078852647225</v>
+        <v>0.08571242200393517</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,79 +5686,79 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.02406957636401721</v>
+        <v>-0.2640891031391868</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2347791196817446</v>
+        <v>0.1310164714227459</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3060440966937655</v>
+        <v>-0.2818086391869219</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.07292669263095368</v>
+        <v>-0.09114309252152986</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.07108207177284283</v>
+        <v>0.1293623639639194</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.03512984166080022</v>
+        <v>-0.13108029027813</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.01071706157227223</v>
+        <v>0.1632104334082835</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.04818194173051956</v>
+        <v>-0.124769410775208</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01719831437864698</v>
+        <v>0.002770588303347321</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1336029322509633</v>
+        <v>0.03926757512521922</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0981748711542383</v>
+        <v>0.1513219501287034</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.01364003803241982</v>
+        <v>0.0985155898076109</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,106 +5767,106 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.02012143978203868</v>
+        <v>-0.01384955240399256</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.06678986653684563</v>
+        <v>0.1020745026287873</v>
       </c>
       <c r="BX10" t="n">
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2008628488143372</v>
+        <v>-0.09151061531895152</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0.04333300002764762</v>
+        <v>0.06241934739344449</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.02524917374634923</v>
+        <v>-0.01279141185920958</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.04674428215802596</v>
+        <v>0.03199707110318688</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01692705989859599</v>
+        <v>0.07612129759143375</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.04337111267044955</v>
+        <v>0.07938833919630821</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.006535169618902433</v>
+        <v>-0.1214499238253945</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.00589203170841813</v>
+        <v>0.04925219063133582</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.08835472818817468</v>
+        <v>-0.03447440309419664</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0.007080762922470431</v>
+        <v>0.004199471624992094</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01300964418173035</v>
+        <v>-0.0003263062192661188</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.04699960513590468</v>
+        <v>-0.00687730946888612</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01273617511166886</v>
+        <v>-0.003456513026455017</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.04768542946037004</v>
+        <v>0.06690414609586838</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
@@ -5875,25 +5875,25 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0320910653177682</v>
+        <v>0.04560845760867098</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.05608590079945903</v>
+        <v>-0.05232039577481721</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.02500922542959883</v>
+        <v>0.14844388517602</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.03172187400351886</v>
+        <v>0.0865211684273824</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5902,79 +5902,79 @@
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0496330581862546</v>
+        <v>-0.2247954435491389</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01999792341894996</v>
+        <v>0.1058155072111857</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.04741995760308487</v>
+        <v>-0.3499129008545556</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.02630381162227558</v>
+        <v>0.1229662244938642</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.01665679452542779</v>
+        <v>0.2062104178954881</v>
       </c>
       <c r="DX10" t="n">
         <v>0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.04771658186455094</v>
+        <v>0.1207563003475922</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.06526674495081949</v>
+        <v>-0.2131226831969096</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.01701490196608371</v>
+        <v>-0.01287909655930971</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.0126106566407458</v>
+        <v>0.05625412696475129</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.1201626040448968</v>
+        <v>0.0002975097264798729</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.07383189437231714</v>
+        <v>0.02890991779811331</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.02320292370688414</v>
+        <v>0.125803364306508</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,133 +5983,133 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.004752949773551092</v>
+        <v>0.1706203486083583</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0.01318201253482148</v>
+        <v>0.04804888414099875</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.05273946409043685</v>
+        <v>0.1001899399718079</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0.006711892380569073</v>
+        <v>0.1484051082444939</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01422983717784029</v>
+        <v>-0.01344056086109102</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0.04901968625297676</v>
+        <v>-0.01328078146766255</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01406108284163863</v>
+        <v>0.01222347542069822</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.04383227311149483</v>
+        <v>0.04314418306593109</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.021745802802035</v>
+        <v>0.1669069909599877</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.007282881318701071</v>
+        <v>0.01059891759742123</v>
       </c>
       <c r="FJ10" t="n">
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02309036521342837</v>
+        <v>0.124799288327287</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0.0450218656514559</v>
+        <v>0.15178423907077</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04124039767393507</v>
+        <v>0.1354356091740737</v>
       </c>
       <c r="FQ10" t="n">
         <v>0</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.05486705948533237</v>
+        <v>-0.1468635676774335</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.07331035396198546</v>
+        <v>-0.009857905485259085</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.03271565205171051</v>
+        <v>0.1995107935955808</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.02375130699669149</v>
+        <v>0.1406981307849748</v>
       </c>
       <c r="FZ10" t="n">
         <v>-0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.009151393063624155</v>
+        <v>-0.02596989012689926</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0.01656186971047223</v>
+        <v>-0.09511013775492082</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1546675942510913</v>
+        <v>0.862205515734986</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02126210846745611</v>
+        <v>0.05595188537673467</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1047622737620331</v>
+        <v>-0.3074591888323676</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,58 +6144,58 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1265215434152772</v>
+        <v>1.071216244399823</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01712544500777572</v>
+        <v>-0.192163146093646</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.09864099295708659</v>
+        <v>-0.2540928824996741</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02345362202690218</v>
+        <v>0.180054365304838</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.006258510307952764</v>
+        <v>-0.1453354131030134</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01389937401049191</v>
+        <v>-0.08467046706319004</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,25 +6204,25 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02056794320201032</v>
+        <v>0.07612210806311277</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01555166770452008</v>
+        <v>-0.4345627046936723</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01303781699059549</v>
+        <v>-0.1728484025988529</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01487888100284751</v>
+        <v>0.2290768753071538</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01017251683732783</v>
+        <v>0.02276801391431074</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04644761929481579</v>
+        <v>-0.216229756843429</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1126933372418174</v>
+        <v>1.206117606455009</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.003752778571858046</v>
+        <v>-0.3793329557132873</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.08230696724791635</v>
+        <v>-0.3534502020255365</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06352977850688123</v>
+        <v>-0.09131547849577162</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.03972620747672272</v>
+        <v>-0.112660344713226</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04567350721875114</v>
+        <v>-0.1339188854003283</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03582709617155534</v>
+        <v>0.1675047752786242</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01417796695441196</v>
+        <v>0.1335678289460321</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01198504704888023</v>
+        <v>-0.004431085409439384</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0603029840838959</v>
+        <v>0.7726702822039672</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.00802793256270347</v>
+        <v>-0.1023713790333547</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.04345017763583505</v>
+        <v>-0.3139412444685138</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6363,25 +6363,25 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03304300130647717</v>
+        <v>-0.3568437276399504</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.001524832659539685</v>
+        <v>0.02729404450377013</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02524023563022688</v>
+        <v>0.2085575497801623</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,52 +6393,52 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.008416190439958223</v>
+        <v>-0.3925741515390364</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.005574811972402139</v>
+        <v>0.2321072459757284</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.006645197955629764</v>
+        <v>0.2642810576494595</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02635472591253795</v>
+        <v>-0.3434834448801116</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.004088492861241183</v>
+        <v>-0.02626607755183868</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02935038719618139</v>
+        <v>0.1873529875538936</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01256766180118058</v>
+        <v>-0.03350358973584507</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.009901627581655317</v>
+        <v>-0.1375699486130388</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02584465314260906</v>
+        <v>0.009319713566669037</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0162633802191667</v>
+        <v>-0.1852120305270251</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03311697523665037</v>
+        <v>0.03926322815402015</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.00106876921918344</v>
+        <v>0.1089989178872163</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,82 +6495,82 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02511534422565461</v>
+        <v>0.07197419264027048</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01068440924701882</v>
+        <v>0.06474414935769907</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01068655702844498</v>
+        <v>-0.1036975270057882</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02051472817755767</v>
+        <v>-0.1080480864988695</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004333907983289259</v>
+        <v>-0.1460563887073101</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.008108703407187499</v>
+        <v>0.07300577779580823</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.01023310577104657</v>
+        <v>-0.1438799491040537</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01111848826806716</v>
+        <v>-0.08607771159764842</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01848929640172172</v>
+        <v>0.08748240634783513</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,37 +6579,37 @@
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02756316614123657</v>
+        <v>-0.3675314952429138</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003879311716973218</v>
+        <v>-0.04374819300461163</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03054540424502026</v>
+        <v>0.1867353114031384</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.004945422237985278</v>
+        <v>-0.3507478153383372</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02593690267025362</v>
+        <v>0.07274186790644595</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03543062432088345</v>
+        <v>0.1914274133008634</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01005088730495977</v>
+        <v>-0.1533189910717515</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008729895723456926</v>
+        <v>0.001499709241489926</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.001478909823683073</v>
+        <v>-0.01166032921179517</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.009243146605927182</v>
+        <v>-0.1506578591013617</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04094291583436825</v>
+        <v>-0.02421440689995874</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,19 +6692,19 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5324287735203928</v>
+        <v>0.4230751639722827</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2301156821186168</v>
+        <v>-0.4045910611977888</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1706958180602797</v>
+        <v>-0.01896042593370813</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6719,16 +6719,16 @@
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4522695295865467</v>
+        <v>0.4615516404239561</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2286709864705714</v>
+        <v>-0.5151888552325241</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2092872253278444</v>
+        <v>-0.01879460164505855</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1080800432186498</v>
+        <v>0.1172242506277225</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.03354693927289628</v>
+        <v>-0.05793671692574184</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05044263195193048</v>
+        <v>-0.2095644816414013</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,25 +6770,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1831444116350047</v>
+        <v>-0.03500794554579045</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-9.293314389110008e-05</v>
+        <v>-0.1736855524548596</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01210667558735372</v>
+        <v>-0.09942951911511676</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,49 +6797,49 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03232926567739231</v>
+        <v>0.1912280106373974</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04133543828274481</v>
+        <v>-0.04713704001473208</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.1069816096953557</v>
+        <v>0.05190769424528179</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5653258575003406</v>
+        <v>0.469154465435744</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.07642357896667763</v>
+        <v>-0.1413270588223071</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.006464714224062563</v>
+        <v>-0.3434912099272534</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08747890055624111</v>
+        <v>-0.1346821702421034</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09553695107257888</v>
+        <v>-0.1703143419081036</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1321489700845621</v>
+        <v>-0.09349471770022084</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1418937170984399</v>
+        <v>0.09076478279416744</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.06131401433052292</v>
+        <v>0.11251761811608</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1832555583886083</v>
+        <v>0.05223560555085697</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3255957904432141</v>
+        <v>0.3426954802537428</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.08032155731969486</v>
+        <v>-0.1771751293111823</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06111838955704734</v>
+        <v>-0.1308932687589228</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1134501497944423</v>
+        <v>-0.1427022323013557</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03357809172072082</v>
+        <v>0.2169764271928028</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01542893489259772</v>
+        <v>0.025180699279005</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,16 +6962,16 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.09852072739853251</v>
+        <v>0.01421235246627369</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04268681357114639</v>
+        <v>0.2338069338449187</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1159798627049141</v>
+        <v>0.1725561845600381</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
@@ -6980,106 +6980,106 @@
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09646970842807608</v>
+        <v>-0.1255297032266124</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.05619163084288868</v>
+        <v>0.2479003681293661</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.008317902736457701</v>
+        <v>0.0432493684908959</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.005948743460585817</v>
+        <v>-0.01012631836456701</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.139413742757327</v>
+        <v>0.05886047165790168</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01626535401681958</v>
+        <v>-0.0123513773377387</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06280835414005739</v>
+        <v>-0.1796207673323157</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.06476042379558489</v>
+        <v>0.1475809110321911</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.1169666142550416</v>
+        <v>0.03668091794762781</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1274503772465284</v>
+        <v>-0.1010108236484269</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.04060955401936148</v>
+        <v>-0.06222655682243006</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.06095033722699003</v>
+        <v>-0.2499252560595851</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09298977397537421</v>
+        <v>-0.05475133196260351</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.08819596092463394</v>
+        <v>0.1671145774902355</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1362992789939556</v>
+        <v>0.04480210788835851</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,19 +7124,19 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.08635255554498034</v>
+        <v>-0.1007462647317533</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03785375153928936</v>
+        <v>0.1506937410208985</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.08483207054247945</v>
+        <v>-0.06106122035381122</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09437893878975721</v>
+        <v>-0.1523255328094203</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.05859372354951367</v>
+        <v>0.2331358355654472</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.03146425714936582</v>
+        <v>0.02019334039491101</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
@@ -7178,16 +7178,16 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.09828374329377089</v>
+        <v>-0.1131480774769905</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05960619601966445</v>
+        <v>0.1588271226254609</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05418686724821322</v>
+        <v>-0.2524368013599355</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7202,25 +7202,25 @@
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01951715581233665</v>
+        <v>-0.02532261214352998</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02750768459415517</v>
+        <v>-0.03867534362354735</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.05041397224363675</v>
+        <v>0.08664258056603417</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7229,28 +7229,28 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.03614722322166748</v>
+        <v>-0.1427136673161296</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03399158875785377</v>
+        <v>0.2397488495499957</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2127481818162456</v>
+        <v>0.1820868116404855</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -7267,25 +7267,25 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1213452895671792</v>
+        <v>-0.2989566295082255</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1442763001557124</v>
+        <v>0.1501311534043056</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2153879649628282</v>
+        <v>0.1242091981658874</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -7294,25 +7294,25 @@
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04883055807025742</v>
+        <v>-0.3911940618787668</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08139647994910056</v>
+        <v>0.08088917127264002</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02999942266900436</v>
+        <v>-0.0174890158040673</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -7321,40 +7321,40 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06181685061295922</v>
+        <v>-0.05008096444047652</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04740348320885432</v>
+        <v>-0.09057651772862954</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.02435029733487662</v>
+        <v>0.05104336633364986</v>
       </c>
       <c r="AC13" t="n">
         <v>-0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.0128775452128222</v>
+        <v>0.06729077181760416</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.007291442668956003</v>
+        <v>0.2639042625378563</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,49 +7363,49 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0009876712400837115</v>
+        <v>0.04776198746971076</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.0151127693234958</v>
+        <v>-0.1583115555908282</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.06589065669835305</v>
+        <v>0.07281410993188218</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.1143883016956932</v>
+        <v>-0.105579273568998</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.05106196232588504</v>
+        <v>-0.3878022344848796</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1637094856704814</v>
+        <v>-0.007108756378489759</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
@@ -7420,7 +7420,7 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.1184517735411994</v>
+        <v>0.1722247511198576</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -7429,37 +7429,37 @@
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.01703979127276205</v>
+        <v>0.253267085789173</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.08761464013488872</v>
+        <v>0.235604142592459</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.02245733433503399</v>
+        <v>-0.02725143334049337</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01721859463317704</v>
+        <v>0.00866922115925582</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0858856748505327</v>
+        <v>-0.1106126519872101</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.05186853012291872</v>
+        <v>-0.07733980043878599</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.002413317766101937</v>
+        <v>-0.3059389286532656</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08014564655202941</v>
+        <v>-0.07416123678708315</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -7495,25 +7495,25 @@
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.04171991599811762</v>
+        <v>-0.06756851683023335</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.01664242001583374</v>
+        <v>0.1130726601047349</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.03108536949131906</v>
+        <v>-0.04973943971068842</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7528,46 +7528,46 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.02003297917815343</v>
+        <v>0.02643852241755306</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.08086158364985026</v>
+        <v>0.1298124110262103</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.09596145660160081</v>
+        <v>-0.09289987475637576</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.03252811021633836</v>
+        <v>-0.06161136108436876</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.001530118247315277</v>
+        <v>0.1150627857850047</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02307518383511102</v>
+        <v>-0.02802864874725379</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7582,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.01613871915039517</v>
+        <v>-0.01580293694054898</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.05611999808322592</v>
+        <v>0.1305031003857235</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.02227689626098308</v>
+        <v>-0.01480581711724752</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7609,79 +7609,79 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.02553801593473321</v>
+        <v>-0.07552734939493638</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.03865860001297722</v>
+        <v>0.02130745326117251</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.08059878124067203</v>
+        <v>-0.01263760687469114</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.03057830847219872</v>
+        <v>0.007701592230680673</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02619243729951997</v>
+        <v>-0.005106664206720535</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02979632934395841</v>
+        <v>-0.010902784612389</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.03790396196512209</v>
+        <v>-0.09824310310737909</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.00812169903954393</v>
+        <v>0.09832822673705081</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.002595699955930855</v>
+        <v>0.01050429385506233</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.01529973682800669</v>
+        <v>0.03478941032003682</v>
       </c>
       <c r="EP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.03378678259352468</v>
+        <v>0.1384870308476897</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.003746849102695152</v>
+        <v>0.001125533422136035</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,19 +7717,19 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.03421373231961227</v>
+        <v>-0.06763122327769286</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.008992436127871475</v>
+        <v>0.1584195273580794</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.03612083700315429</v>
+        <v>-0.04015520613218932</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.002836140414838229</v>
+        <v>0.03832153186499044</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
@@ -7753,25 +7753,25 @@
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01319877608197048</v>
+        <v>0.1294019439214459</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1215513789028884</v>
+        <v>0.1183313390603556</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01261423274869531</v>
+        <v>-0.003919507644915285</v>
       </c>
       <c r="FQ13" t="n">
         <v>-0</v>
@@ -7780,40 +7780,40 @@
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.001491104576589455</v>
+        <v>0.2597925146339439</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.04911029474173853</v>
+        <v>0.04884986276619438</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02150251150644242</v>
+        <v>0.02934259410116799</v>
       </c>
       <c r="FZ13" t="n">
         <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.02436690417023375</v>
+        <v>0.2226689116898729</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8968,49 +8968,49 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4798839090221421</v>
+        <v>0.09781335023102454</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08739983253848428</v>
+        <v>-0.05356516483728394</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09708317245157393</v>
+        <v>-0.02696676208968503</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3060445113342578</v>
+        <v>0.1189157520509654</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1350739504912112</v>
+        <v>-0.08893703225860895</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1071874458000956</v>
+        <v>-0.07927083328176937</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,70 +9022,70 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08637900757558158</v>
+        <v>0.02621841888448643</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03067475875928937</v>
+        <v>-0.0242807791456515</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1364408273779457</v>
+        <v>-0.02213579554419083</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.08478549621922067</v>
+        <v>-0.006480965362691084</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.03401267868909055</v>
+        <v>-0.08646441662069314</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.04946780163147248</v>
+        <v>-0.07482000844443749</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.02788074677289032</v>
+        <v>0.06423320975726951</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.03198605229156495</v>
+        <v>-0.05096219480844606</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.007508879044618359</v>
+        <v>0.03153403222681542</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
@@ -9094,34 +9094,34 @@
         <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.347499857733591</v>
+        <v>0.1206287412802079</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.258758525554364e-10</v>
+        <v>-8.75565864546064e-12</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1068424098300194</v>
+        <v>-0.1210802734723876</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.04515492095906791</v>
+        <v>-0.02010081856790463</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.1920996426943725</v>
+        <v>-0.03640814720156724</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1484162654406598</v>
+        <v>-0.02375498659037251</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,16 +9157,16 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1065096399426149</v>
+        <v>0.0408905623672351</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.01319023133283461</v>
+        <v>0.03477881622612052</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1604846170122597</v>
+        <v>0.04716300015388619</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
@@ -9178,76 +9178,76 @@
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1712898781336678</v>
+        <v>0.09677934211594277</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.08290813412540324</v>
+        <v>-0.03948292081902184</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.08901966590799887</v>
+        <v>-0.0264167518776986</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.08712596943517655</v>
+        <v>-0.02676799093335626</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0.02075387597562721</v>
+        <v>0.04205193001518072</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.002153592644940722</v>
+        <v>0.0238498129406562</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.009864816534725694</v>
+        <v>-0.05938086061811994</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.1467870035899039</v>
+        <v>0.1101220236548168</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.0920787933183824</v>
+        <v>0.0705938637480866</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9262,46 +9262,46 @@
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.05791724556515188</v>
+        <v>-0.01820059613746765</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.005182475415450661</v>
+        <v>0.04466092199792888</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.009156336064185575</v>
+        <v>0.03033653692151704</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.05148853160773132</v>
+        <v>0.013549590805553</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.05085688338474276</v>
+        <v>-0.004935619158459729</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05731869786103624</v>
+        <v>-0.04702293530910167</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,19 +9316,19 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.06921948725479179</v>
+        <v>-0.05096934750060964</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.003288009373436834</v>
+        <v>-0.027779410375552</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.0501321460496245</v>
+        <v>0.01342096848859628</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -9337,7 +9337,7 @@
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,16 +9346,16 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.03861324932848842</v>
+        <v>0.005294199331168553</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.03957069134164235</v>
+        <v>0.0287066719788586</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.01956103109405261</v>
+        <v>0.008704220890404176</v>
       </c>
       <c r="EB16" t="n">
         <v>-0</v>
@@ -9364,52 +9364,52 @@
         <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.07212848662979884</v>
+        <v>0.01297632738639439</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.02466539543301993</v>
+        <v>0.02199403092799864</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0880462334578923</v>
+        <v>0.05371389451692393</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.002182189181602288</v>
+        <v>-0.001602677021559571</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01246032849560602</v>
+        <v>0.03711416003971459</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02266190414171212</v>
+        <v>-0.01254368410268342</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.05761992190603876</v>
+        <v>-0.02450219310320065</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.02902193069762792</v>
+        <v>0.05928252199841839</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.01034691459685499</v>
+        <v>0.01677992134610695</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
@@ -9445,85 +9445,85 @@
         <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.004955513465100514</v>
+        <v>0.02994071039930106</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0.007035758394658607</v>
+        <v>0.01559399620951297</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.005592818130360866</v>
+        <v>0.01353394389337711</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.0419248616880936</v>
+        <v>0.01303524553380487</v>
       </c>
       <c r="FR16" t="n">
         <v>0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.03124223524113894</v>
+        <v>0.02622348904660303</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.03073948573563783</v>
+        <v>-0.0550588781792862</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.03075002026424319</v>
+        <v>0.02088309685760888</v>
       </c>
       <c r="GA16" t="n">
         <v>-0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.101573470512779</v>
+        <v>-0.007907131696458528</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
